--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7398,0.0868,0.0249,0.0459</t>
-  </si>
-  <si>
-    <t>0.6534,0.0478,0.0379,0.1979</t>
-  </si>
-  <si>
-    <t>0.7279,0.1287,0.0457,0.0460</t>
-  </si>
-  <si>
-    <t>0.8355,0.0656,0.0130,0.0241</t>
-  </si>
-  <si>
-    <t>0.5290,0.3332,0.0247,0.0281</t>
-  </si>
-  <si>
-    <t>0.8037,0.0418,0.0065,0.0362</t>
-  </si>
-  <si>
-    <t>0.6279,0.2787,0.0482,0.0184</t>
-  </si>
-  <si>
-    <t>0.7742,0.1459,0.0126,0.0140</t>
-  </si>
-  <si>
-    <t>0.6985,0.1180,0.0322,0.0516</t>
-  </si>
-  <si>
-    <t>0.6852,0.1163,0.0168,0.0325</t>
-  </si>
-  <si>
-    <t>0.4866,0.3104,0.0762,0.0572</t>
-  </si>
-  <si>
-    <t>0.7245,0.0488,0.0156,0.1001</t>
-  </si>
-  <si>
-    <t>0.7855,0.0735,0.0847,0.0406</t>
-  </si>
-  <si>
-    <t>0.9149,0.0070,0.0187,0.0299</t>
-  </si>
-  <si>
-    <t>0.7503,0.0083,0.1959,0.0370</t>
-  </si>
-  <si>
-    <t>0.6790,0.0506,0.3019,0.0267</t>
-  </si>
-  <si>
-    <t>0.8659,0.0434,0.0250,0.0245</t>
-  </si>
-  <si>
-    <t>0.0165,0.9696,0.0259,0.0077</t>
-  </si>
-  <si>
-    <t>0.4068,0.5403,0.0114,0.0093</t>
-  </si>
-  <si>
-    <t>0.5481,0.3201,0.0199,0.0163</t>
-  </si>
-  <si>
-    <t>0.0570,0.8917,0.0726,0.0277</t>
-  </si>
-  <si>
-    <t>0.0207,0.9666,0.0105,0.0073</t>
-  </si>
-  <si>
-    <t>0.8921,0.0297,0.0281,0.0141</t>
-  </si>
-  <si>
-    <t>0.9304,0.0062,0.0195,0.0184</t>
-  </si>
-  <si>
-    <t>0.8453,0.0120,0.1678,0.0024</t>
-  </si>
-  <si>
-    <t>0.9180,0.0115,0.0321,0.0165</t>
-  </si>
-  <si>
-    <t>0.8441,0.0096,0.1656,0.0109</t>
-  </si>
-  <si>
-    <t>0.7733,0.0287,0.1997,0.0230</t>
-  </si>
-  <si>
-    <t>0.3208,0.1999,0.6329,0.0185</t>
-  </si>
-  <si>
-    <t>0.5231,0.2771,0.0182,0.0339</t>
-  </si>
-  <si>
-    <t>0.7496,0.0541,0.0359,0.0849</t>
-  </si>
-  <si>
-    <t>0.0170,0.5630,0.9540,0.0032</t>
-  </si>
-  <si>
-    <t>0.5280,0.2792,0.2508,0.0287</t>
-  </si>
-  <si>
-    <t>0.7527,0.0803,0.0148,0.0361</t>
-  </si>
-  <si>
-    <t>0.6127,0.1489,0.1275,0.1248</t>
-  </si>
-  <si>
-    <t>0.7208,0.1072,0.0099,0.0362</t>
-  </si>
-  <si>
-    <t>0.4455,0.3865,0.0350,0.0162</t>
-  </si>
-  <si>
-    <t>0.4624,0.3065,0.0905,0.0835</t>
-  </si>
-  <si>
-    <t>0.6181,0.0081,0.3126,0.0387</t>
-  </si>
-  <si>
-    <t>0.5773,0.0304,0.4646,0.0053</t>
-  </si>
-  <si>
-    <t>0.9405,0.0092,0.0333,0.0080</t>
-  </si>
-  <si>
-    <t>0.5138,0.1242,0.3868,0.0256</t>
-  </si>
-  <si>
-    <t>0.5587,0.4780,0.0212,0.0092</t>
-  </si>
-  <si>
-    <t>0.7701,0.0141,0.2676,0.0089</t>
-  </si>
-  <si>
-    <t>0.7337,0.0456,0.0134,0.1059</t>
-  </si>
-  <si>
-    <t>0.7896,0.1382,0.0091,0.0116</t>
-  </si>
-  <si>
-    <t>0.3384,0.5290,0.0184,0.0230</t>
-  </si>
-  <si>
-    <t>0.4537,0.4437,0.0393,0.0162</t>
-  </si>
-  <si>
-    <t>0.0572,0.3230,0.8809,0.0075</t>
-  </si>
-  <si>
-    <t>0.2222,0.1363,0.7759,0.0074</t>
-  </si>
-  <si>
-    <t>0.7458,0.0201,0.2365,0.0177</t>
-  </si>
-  <si>
-    <t>0.5972,0.0246,0.4362,0.0127</t>
-  </si>
-  <si>
-    <t>0.3956,0.0813,0.6713,0.0081</t>
-  </si>
-  <si>
-    <t>0.5089,0.0804,0.5292,0.0058</t>
-  </si>
-  <si>
-    <t>0.7452,0.1333,0.0158,0.0223</t>
-  </si>
-  <si>
-    <t>0.7912,0.1463,0.0099,0.0109</t>
-  </si>
-  <si>
-    <t>0.7450,0.0671,0.0075,0.0384</t>
-  </si>
-  <si>
-    <t>0.1008,0.7246,0.6335,0.0330</t>
-  </si>
-  <si>
-    <t>0.6769,0.1095,0.0165,0.0495</t>
-  </si>
-  <si>
-    <t>0.7284,0.0718,0.0159,0.0636</t>
-  </si>
-  <si>
-    <t>0.8817,0.0563,0.0122,0.0132</t>
-  </si>
-  <si>
-    <t>0.0028,0.9496,0.9245,0.0016</t>
-  </si>
-  <si>
-    <t>0.6352,0.0288,0.3889,0.0065</t>
-  </si>
-  <si>
-    <t>0.2179,0.3033,0.6094,0.0049</t>
-  </si>
-  <si>
-    <t>0.2038,0.5412,0.4535,0.0053</t>
-  </si>
-  <si>
-    <t>0.0266,0.0107,0.9821,0.0005</t>
-  </si>
-  <si>
-    <t>0.4712,0.3736,0.0543,0.0228</t>
-  </si>
-  <si>
-    <t>0.0224,0.9720,0.0307,0.0058</t>
-  </si>
-  <si>
-    <t>0.8760,0.0535,0.0136,0.0161</t>
-  </si>
-  <si>
-    <t>0.8360,0.0276,0.0300,0.0638</t>
-  </si>
-  <si>
-    <t>0.0226,0.6691,0.9086,0.0035</t>
-  </si>
-  <si>
-    <t>0.0866,0.6875,0.7010,0.0074</t>
-  </si>
-  <si>
-    <t>0.6237,0.0755,0.3566,0.0045</t>
-  </si>
-  <si>
-    <t>0.0051,0.9628,0.8235,0.0019</t>
-  </si>
-  <si>
-    <t>0.0049,0.9535,0.8786,0.0010</t>
-  </si>
-  <si>
-    <t>0.8865,0.0166,0.0425,0.0263</t>
-  </si>
-  <si>
-    <t>0.6009,0.0348,0.0102,0.2271</t>
-  </si>
-  <si>
-    <t>0.8368,0.0539,0.0184,0.0472</t>
-  </si>
-  <si>
-    <t>0.8222,0.0306,0.0107,0.0571</t>
-  </si>
-  <si>
-    <t>0.7714,0.0314,0.0311,0.1364</t>
-  </si>
-  <si>
-    <t>0.5375,0.0790,0.0466,0.2533</t>
-  </si>
-  <si>
-    <t>0.0132,0.7815,0.9197,0.0021</t>
-  </si>
-  <si>
-    <t>0.2654,0.0143,0.8286,0.0022</t>
-  </si>
-  <si>
-    <t>0.6952,0.0506,0.2833,0.0055</t>
-  </si>
-  <si>
-    <t>0.1229,0.0779,0.8865,0.0033</t>
-  </si>
-  <si>
-    <t>0.0143,0.8884,0.8377,0.0030</t>
-  </si>
-  <si>
-    <t>0.6575,0.1603,0.1262,0.0168</t>
-  </si>
-  <si>
-    <t>0.4852,0.2161,0.0164,0.0456</t>
-  </si>
-  <si>
-    <t>0.8121,0.0581,0.0101,0.0276</t>
-  </si>
-  <si>
-    <t>0.7818,0.0246,0.0029,0.0619</t>
-  </si>
-  <si>
-    <t>0.8085,0.0280,0.0061,0.0624</t>
-  </si>
-  <si>
-    <t>0.8970,0.0265,0.0041,0.0173</t>
-  </si>
-  <si>
-    <t>0.7579,0.1336,0.0056,0.0092</t>
-  </si>
-  <si>
-    <t>0.7841,0.0664,0.0149,0.0391</t>
-  </si>
-  <si>
-    <t>0.7102,0.0998,0.0098,0.0338</t>
-  </si>
-  <si>
-    <t>0.4202,0.2871,0.0240,0.0479</t>
-  </si>
-  <si>
-    <t>0.7590,0.0822,0.0121,0.0366</t>
-  </si>
-  <si>
-    <t>0.8619,0.0400,0.0046,0.0186</t>
-  </si>
-  <si>
-    <t>0.7958,0.0378,0.0089,0.0560</t>
-  </si>
-  <si>
-    <t>0.8453,0.0548,0.0104,0.0202</t>
-  </si>
-  <si>
-    <t>0.7578,0.0894,0.0249,0.0577</t>
-  </si>
-  <si>
-    <t>0.5583,0.3181,0.0386,0.0217</t>
-  </si>
-  <si>
-    <t>0.8244,0.0634,0.0069,0.0185</t>
-  </si>
-  <si>
-    <t>0.4331,0.0430,0.6060,0.0168</t>
-  </si>
-  <si>
-    <t>0.8332,0.0153,0.1386,0.0103</t>
-  </si>
-  <si>
-    <t>0.8344,0.0160,0.0473,0.0600</t>
-  </si>
-  <si>
-    <t>0.3803,0.0292,0.6341,0.0143</t>
-  </si>
-  <si>
-    <t>0.0991,0.7679,0.0528,0.0508</t>
-  </si>
-  <si>
-    <t>0.5072,0.4663,0.0185,0.0109</t>
-  </si>
-  <si>
-    <t>0.6221,0.1566,0.0145,0.0366</t>
-  </si>
-  <si>
-    <t>0.1334,0.6539,0.0335,0.0628</t>
-  </si>
-  <si>
-    <t>0.4234,0.4953,0.0483,0.0237</t>
-  </si>
-  <si>
-    <t>0.0802,0.8743,0.0729,0.0165</t>
-  </si>
-  <si>
-    <t>0.7604,0.1474,0.0288,0.0183</t>
-  </si>
-  <si>
-    <t>0.8433,0.0417,0.0198,0.0450</t>
-  </si>
-  <si>
-    <t>0.8270,0.0176,0.0889,0.0641</t>
-  </si>
-  <si>
-    <t>0.7065,0.1443,0.0440,0.0249</t>
-  </si>
-  <si>
-    <t>0.9394,0.0192,0.0152,0.0070</t>
-  </si>
-  <si>
-    <t>0.7449,0.0523,0.0292,0.0743</t>
-  </si>
-  <si>
-    <t>0.1591,0.8277,0.0537,0.0072</t>
-  </si>
-  <si>
-    <t>0.1098,0.8680,0.0868,0.0121</t>
-  </si>
-  <si>
-    <t>0.0433,0.9175,0.1751,0.0152</t>
-  </si>
-  <si>
-    <t>0.0687,0.7465,0.7038,0.0129</t>
-  </si>
-  <si>
-    <t>0.5507,0.2943,0.0261,0.0172</t>
-  </si>
-  <si>
-    <t>0.6366,0.1492,0.0254,0.0365</t>
-  </si>
-  <si>
-    <t>0.6963,0.1830,0.0222,0.0262</t>
-  </si>
-  <si>
-    <t>0.7697,0.0982,0.0125,0.0207</t>
-  </si>
-  <si>
-    <t>0.8345,0.0306,0.0177,0.0757</t>
-  </si>
-  <si>
-    <t>0.7209,0.0834,0.0066,0.0318</t>
-  </si>
-  <si>
-    <t>0.6840,0.0805,0.0274,0.0906</t>
-  </si>
-  <si>
-    <t>0.8453,0.0633,0.0234,0.0333</t>
-  </si>
-  <si>
-    <t>0.7315,0.1274,0.0248,0.0311</t>
-  </si>
-  <si>
-    <t>0.7436,0.0583,0.0345,0.0923</t>
-  </si>
-  <si>
-    <t>0.6626,0.1093,0.0224,0.0672</t>
-  </si>
-  <si>
-    <t>0.0612,0.5695,0.8299,0.0035</t>
-  </si>
-  <si>
-    <t>0.3618,0.1563,0.5779,0.0063</t>
-  </si>
-  <si>
-    <t>0.4402,0.0580,0.6049,0.0028</t>
-  </si>
-  <si>
-    <t>0.4377,0.1163,0.5048,0.0111</t>
-  </si>
-  <si>
-    <t>0.9438,0.0105,0.0153,0.0088</t>
-  </si>
-  <si>
-    <t>0.8590,0.0464,0.0420,0.0327</t>
-  </si>
-  <si>
-    <t>0.7920,0.0554,0.0366,0.0635</t>
-  </si>
-  <si>
-    <t>0.8777,0.0640,0.0093,0.0113</t>
-  </si>
-  <si>
-    <t>0.7862,0.0159,0.0030,0.0783</t>
-  </si>
-  <si>
-    <t>0.7222,0.0218,0.0088,0.1751</t>
-  </si>
-  <si>
-    <t>0.9043,0.0125,0.0048,0.0361</t>
-  </si>
-  <si>
-    <t>0.8443,0.0399,0.0097,0.0279</t>
-  </si>
-  <si>
-    <t>0.0219,0.8962,0.6937,0.0110</t>
-  </si>
-  <si>
-    <t>0.7180,0.2002,0.0133,0.0122</t>
-  </si>
-  <si>
-    <t>0.7614,0.0829,0.0092,0.0277</t>
-  </si>
-  <si>
-    <t>0.6558,0.0567,0.0158,0.1373</t>
-  </si>
-  <si>
-    <t>0.7936,0.0298,0.0047,0.0589</t>
-  </si>
-  <si>
-    <t>0.8387,0.0185,0.0123,0.1150</t>
-  </si>
-  <si>
-    <t>0.9354,0.0113,0.0008,0.0113</t>
-  </si>
-  <si>
-    <t>0.7204,0.1547,0.0196,0.0276</t>
-  </si>
-  <si>
-    <t>0.0265,0.6943,0.9021,0.0120</t>
-  </si>
-  <si>
-    <t>0.8550,0.0259,0.0052,0.0375</t>
-  </si>
-  <si>
-    <t>0.7837,0.0484,0.0095,0.0431</t>
-  </si>
-  <si>
-    <t>0.6269,0.1607,0.0190,0.0422</t>
-  </si>
-  <si>
-    <t>0.7733,0.0882,0.0203,0.0256</t>
-  </si>
-  <si>
-    <t>0.8360,0.0206,0.0082,0.0576</t>
-  </si>
-  <si>
-    <t>0.7645,0.1246,0.0348,0.0256</t>
-  </si>
-  <si>
-    <t>0.6587,0.2500,0.0414,0.0176</t>
-  </si>
-  <si>
-    <t>0.6781,0.1610,0.0509,0.0452</t>
-  </si>
-  <si>
-    <t>0.6173,0.0701,0.0123,0.1054</t>
-  </si>
-  <si>
-    <t>0.8861,0.0129,0.0043,0.0458</t>
-  </si>
-  <si>
-    <t>0.8743,0.0562,0.0051,0.0104</t>
-  </si>
-  <si>
-    <t>0.8051,0.0650,0.0167,0.0342</t>
-  </si>
-  <si>
-    <t>0.8493,0.0269,0.0043,0.0292</t>
-  </si>
-  <si>
-    <t>0.8010,0.1117,0.0085,0.0100</t>
-  </si>
-  <si>
-    <t>0.8393,0.0404,0.0073,0.0269</t>
-  </si>
-  <si>
-    <t>0.8682,0.0304,0.0078,0.0283</t>
-  </si>
-  <si>
-    <t>0.4100,0.4035,0.0409,0.0289</t>
-  </si>
-  <si>
-    <t>0.6088,0.1093,0.0071,0.0406</t>
-  </si>
-  <si>
-    <t>0.7068,0.1884,0.0254,0.0238</t>
-  </si>
-  <si>
-    <t>0.8134,0.0491,0.0385,0.0682</t>
-  </si>
-  <si>
-    <t>0.4970,0.2860,0.0607,0.0752</t>
-  </si>
-  <si>
-    <t>0.7652,0.0717,0.0203,0.0423</t>
-  </si>
-  <si>
-    <t>0.6116,0.2485,0.0261,0.0238</t>
-  </si>
-  <si>
-    <t>0.7564,0.1049,0.0138,0.0197</t>
-  </si>
-  <si>
-    <t>0.0234,0.4472,0.9441,0.0027</t>
-  </si>
-  <si>
-    <t>0.6779,0.1026,0.0233,0.0711</t>
-  </si>
-  <si>
-    <t>0.0967,0.0186,0.9486,0.0009</t>
-  </si>
-  <si>
-    <t>0.7398,0.0911,0.1800,0.0289</t>
-  </si>
-  <si>
-    <t>0.6741,0.0867,0.1722,0.0407</t>
-  </si>
-  <si>
-    <t>0.2072,0.1098,0.7820,0.0065</t>
-  </si>
-  <si>
-    <t>0.1282,0.1101,0.8795,0.0033</t>
-  </si>
-  <si>
-    <t>0.6567,0.0551,0.3242,0.0158</t>
-  </si>
-  <si>
-    <t>0.1824,0.1414,0.7975,0.0119</t>
-  </si>
-  <si>
-    <t>0.5709,0.1969,0.2004,0.0638</t>
-  </si>
-  <si>
-    <t>0.7044,0.0215,0.2639,0.0425</t>
-  </si>
-  <si>
-    <t>0.8080,0.0499,0.0900,0.0486</t>
-  </si>
-  <si>
-    <t>0.7329,0.1283,0.0557,0.0380</t>
-  </si>
-  <si>
-    <t>0.9253,0.0179,0.0076,0.0159</t>
-  </si>
-  <si>
-    <t>0.7666,0.0912,0.0587,0.0493</t>
-  </si>
-  <si>
-    <t>0.8809,0.0294,0.0204,0.0353</t>
-  </si>
-  <si>
-    <t>0.8351,0.0246,0.0318,0.0665</t>
-  </si>
-  <si>
-    <t>0.5582,0.4507,0.0183,0.0058</t>
-  </si>
-  <si>
-    <t>0.6037,0.3361,0.0234,0.0116</t>
-  </si>
-  <si>
-    <t>0.7335,0.1471,0.0165,0.0196</t>
-  </si>
-  <si>
-    <t>0.6942,0.1208,0.0063,0.0213</t>
-  </si>
-  <si>
-    <t>0.7205,0.0981,0.0083,0.0214</t>
-  </si>
-  <si>
-    <t>0.8180,0.0373,0.0138,0.0485</t>
-  </si>
-  <si>
-    <t>0.9456,0.0067,0.0096,0.0124</t>
-  </si>
-  <si>
-    <t>0.8893,0.0371,0.0313,0.0144</t>
-  </si>
-  <si>
-    <t>0.8839,0.0353,0.0152,0.0111</t>
-  </si>
-  <si>
-    <t>0.9088,0.0282,0.0139,0.0110</t>
-  </si>
-  <si>
-    <t>0.2522,0.0482,0.7542,0.0110</t>
-  </si>
-  <si>
-    <t>0.7898,0.0316,0.1559,0.0247</t>
-  </si>
-  <si>
-    <t>0.9026,0.0192,0.0314,0.0142</t>
-  </si>
-  <si>
-    <t>0.6408,0.0487,0.3337,0.0137</t>
-  </si>
-  <si>
-    <t>0.7187,0.0474,0.2391,0.0062</t>
-  </si>
-  <si>
-    <t>0.7359,0.0411,0.0093,0.0662</t>
-  </si>
-  <si>
-    <t>0.6739,0.2397,0.0213,0.0150</t>
-  </si>
-  <si>
-    <t>0.8310,0.1208,0.0088,0.0103</t>
-  </si>
-  <si>
-    <t>0.5549,0.1750,0.0285,0.0680</t>
-  </si>
-  <si>
-    <t>0.8193,0.0718,0.0091,0.0153</t>
-  </si>
-  <si>
-    <t>0.9215,0.0123,0.0021,0.0151</t>
-  </si>
-  <si>
-    <t>0.6913,0.1699,0.0102,0.0192</t>
-  </si>
-  <si>
-    <t>0.7640,0.0681,0.0056,0.0307</t>
-  </si>
-  <si>
-    <t>0.7793,0.0617,0.0891,0.0619</t>
-  </si>
-  <si>
-    <t>0.9039,0.0233,0.0102,0.0217</t>
-  </si>
-  <si>
-    <t>0.7758,0.0543,0.0277,0.0635</t>
-  </si>
-  <si>
-    <t>0.1128,0.0306,0.9371,0.0008</t>
-  </si>
-  <si>
-    <t>0.2851,0.0279,0.7515,0.0174</t>
-  </si>
-  <si>
-    <t>0.8383,0.0265,0.1242,0.0119</t>
-  </si>
-  <si>
-    <t>0.0631,0.0238,0.9699,0.0007</t>
-  </si>
-  <si>
-    <t>0.4459,0.0831,0.5410,0.0147</t>
-  </si>
-  <si>
-    <t>0.0574,0.0996,0.9169,0.0080</t>
-  </si>
-  <si>
-    <t>0.8049,0.0044,0.2617,0.0041</t>
-  </si>
-  <si>
-    <t>0.0779,0.2180,0.8146,0.0136</t>
-  </si>
-  <si>
-    <t>0.8234,0.0378,0.0449,0.0364</t>
-  </si>
-  <si>
-    <t>0.9154,0.0202,0.0358,0.0041</t>
-  </si>
-  <si>
-    <t>0.9378,0.0133,0.0134,0.0097</t>
-  </si>
-  <si>
-    <t>0.8113,0.0432,0.0134,0.0604</t>
-  </si>
-  <si>
-    <t>0.8778,0.0398,0.0032,0.0125</t>
-  </si>
-  <si>
-    <t>0.8764,0.0378,0.0079,0.0274</t>
-  </si>
-  <si>
-    <t>0.8036,0.0760,0.0107,0.0210</t>
-  </si>
-  <si>
-    <t>0.8430,0.0476,0.0054,0.0154</t>
-  </si>
-  <si>
-    <t>0.6696,0.0965,0.0088,0.0483</t>
-  </si>
-  <si>
-    <t>0.8575,0.0282,0.0073,0.0462</t>
-  </si>
-  <si>
-    <t>0.7534,0.0457,0.0048,0.0355</t>
-  </si>
-  <si>
-    <t>0.7654,0.0709,0.1182,0.0137</t>
-  </si>
-  <si>
-    <t>0.0037,0.4239,0.9884,0.0002</t>
-  </si>
-  <si>
-    <t>0.2848,0.0719,0.7066,0.0210</t>
-  </si>
-  <si>
-    <t>0.7607,0.0263,0.1890,0.0325</t>
-  </si>
-  <si>
-    <t>0.2393,0.0183,0.8403,0.0024</t>
-  </si>
-  <si>
-    <t>0.8723,0.0367,0.0544,0.0208</t>
-  </si>
-  <si>
-    <t>0.8042,0.0447,0.1055,0.0208</t>
-  </si>
-  <si>
-    <t>0.1683,0.0086,0.5088,0.1273</t>
-  </si>
-  <si>
-    <t>0.9161,0.0286,0.0057,0.0077</t>
-  </si>
-  <si>
-    <t>0.7143,0.0233,0.0200,0.2115</t>
-  </si>
-  <si>
-    <t>0.7878,0.0110,0.0061,0.1649</t>
-  </si>
-  <si>
-    <t>0.8039,0.0279,0.0197,0.1197</t>
-  </si>
-  <si>
-    <t>0.8605,0.0034,0.0073,0.1349</t>
-  </si>
-  <si>
-    <t>0.8762,0.0344,0.0210,0.0229</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9932,0.0010,0.0009,0.0016</t>
+  </si>
+  <si>
+    <t>0.0125,0.0005,0.0007,0.9955</t>
+  </si>
+  <si>
+    <t>0.7105,0.0006,0.0027,0.4639</t>
+  </si>
+  <si>
+    <t>0.4123,0.0026,0.0028,0.7820</t>
+  </si>
+  <si>
+    <t>0.9949,0.0014,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9961,0.0005,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9938,0.0019,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9925,0.0013,0.0006,0.0024</t>
+  </si>
+  <si>
+    <t>0.9968,0.0006,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9773,0.0354,0.0016,0.0004</t>
+  </si>
+  <si>
+    <t>0.9969,0.0004,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9973,0.0007,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9597,0.0014,0.0614,0.0005</t>
+  </si>
+  <si>
+    <t>0.0200,0.0120,0.9804,0.0010</t>
+  </si>
+  <si>
+    <t>0.6842,0.0024,0.6007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0298,0.0046,0.9692,0.0014</t>
+  </si>
+  <si>
+    <t>0.9478,0.0039,0.0556,0.0035</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.0253,0.9681,0.0030,0.0015</t>
+  </si>
+  <si>
+    <t>0.0039,0.9907,0.0067,0.0021</t>
+  </si>
+  <si>
+    <t>0.0030,0.9940,0.0037,0.0003</t>
+  </si>
+  <si>
+    <t>0.6619,0.0083,0.4806,0.0040</t>
+  </si>
+  <si>
+    <t>0.0548,0.0078,0.9364,0.0055</t>
+  </si>
+  <si>
+    <t>0.0064,0.0019,0.9918,0.0014</t>
+  </si>
+  <si>
+    <t>0.0212,0.0239,0.9538,0.0016</t>
+  </si>
+  <si>
+    <t>0.0171,0.0371,0.9575,0.0059</t>
+  </si>
+  <si>
+    <t>0.0105,0.0043,0.9819,0.0012</t>
+  </si>
+  <si>
+    <t>0.0158,0.0032,0.9633,0.0265</t>
+  </si>
+  <si>
+    <t>0.1273,0.8541,0.0249,0.0022</t>
+  </si>
+  <si>
+    <t>0.2388,0.0709,0.7997,0.0150</t>
+  </si>
+  <si>
+    <t>0.0006,0.0036,0.9984,0.0004</t>
+  </si>
+  <si>
+    <t>0.0294,0.9159,0.0497,0.0009</t>
+  </si>
+  <si>
+    <t>0.7956,0.0964,0.1056,0.0441</t>
+  </si>
+  <si>
+    <t>0.2219,0.0086,0.7992,0.0078</t>
+  </si>
+  <si>
+    <t>0.4721,0.6962,0.0043,0.0005</t>
+  </si>
+  <si>
+    <t>0.0084,0.9735,0.3925,0.0015</t>
+  </si>
+  <si>
+    <t>0.0529,0.3700,0.5849,0.0044</t>
+  </si>
+  <si>
+    <t>0.1862,0.0007,0.7080,0.0205</t>
+  </si>
+  <si>
+    <t>0.0229,0.0468,0.9596,0.0044</t>
+  </si>
+  <si>
+    <t>0.4139,0.0027,0.8091,0.0012</t>
+  </si>
+  <si>
+    <t>0.0032,0.0382,0.9906,0.0018</t>
+  </si>
+  <si>
+    <t>0.0094,0.9861,0.0078,0.0005</t>
+  </si>
+  <si>
+    <t>0.0231,0.0022,0.9839,0.0005</t>
+  </si>
+  <si>
+    <t>0.0119,0.8303,0.0064,0.7320</t>
+  </si>
+  <si>
+    <t>0.0038,0.9898,0.0057,0.0028</t>
+  </si>
+  <si>
+    <t>0.0005,0.9976,0.0072,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.9943,0.0123,0.0041</t>
+  </si>
+  <si>
+    <t>0.0023,0.0152,0.9895,0.0037</t>
+  </si>
+  <si>
+    <t>0.0024,0.1112,0.9793,0.0015</t>
+  </si>
+  <si>
+    <t>0.0058,0.0096,0.9918,0.0005</t>
+  </si>
+  <si>
+    <t>0.0375,0.0024,0.9696,0.0031</t>
+  </si>
+  <si>
+    <t>0.0024,0.0068,0.9893,0.0081</t>
+  </si>
+  <si>
+    <t>0.0460,0.0299,0.9531,0.0012</t>
+  </si>
+  <si>
+    <t>0.9935,0.0043,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9891,0.0021,0.0059,0.0013</t>
+  </si>
+  <si>
+    <t>0.9822,0.0037,0.0077,0.0040</t>
+  </si>
+  <si>
+    <t>0.0060,0.0070,0.9847,0.0143</t>
+  </si>
+  <si>
+    <t>0.9949,0.0007,0.0010,0.0012</t>
+  </si>
+  <si>
+    <t>0.9963,0.0017,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9567,0.0539,0.0054,0.0012</t>
+  </si>
+  <si>
+    <t>0.0002,0.9398,0.9880,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0867,0.9893,0.0012</t>
+  </si>
+  <si>
+    <t>0.0013,0.0013,0.9965,0.0013</t>
+  </si>
+  <si>
+    <t>0.0017,0.6448,0.9754,0.0021</t>
+  </si>
+  <si>
+    <t>0.0007,0.0007,0.9983,0.0005</t>
+  </si>
+  <si>
+    <t>0.0042,0.9938,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.9965,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.6028,0.0045,0.6734,0.0010</t>
+  </si>
+  <si>
+    <t>0.0342,0.2694,0.9077,0.0096</t>
+  </si>
+  <si>
+    <t>0.0006,0.0017,0.9983,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9118,0.9843,0.0004</t>
+  </si>
+  <si>
+    <t>0.0022,0.5385,0.9506,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9983,0.3549,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9945,0.7974,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.0004,0.0483,0.9780</t>
+  </si>
+  <si>
+    <t>0.0006,0.0074,0.0013,0.9988</t>
+  </si>
+  <si>
+    <t>0.0018,0.0005,0.0005,0.9988</t>
+  </si>
+  <si>
+    <t>0.0055,0.0064,0.0012,0.9964</t>
+  </si>
+  <si>
+    <t>0.0083,0.0005,0.0032,0.9941</t>
+  </si>
+  <si>
+    <t>0.0056,0.0050,0.0075,0.9926</t>
+  </si>
+  <si>
+    <t>0.0004,0.9877,0.6614,0.0001</t>
+  </si>
+  <si>
+    <t>0.0059,0.5010,0.9605,0.0008</t>
+  </si>
+  <si>
+    <t>0.0016,0.8294,0.9660,0.0010</t>
+  </si>
+  <si>
+    <t>0.0024,0.9355,0.8726,0.0010</t>
+  </si>
+  <si>
+    <t>0.0005,0.7105,0.9813,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9846,0.5234,0.0005</t>
+  </si>
+  <si>
+    <t>0.9958,0.0015,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9783,0.0133,0.0014,0.0030</t>
+  </si>
+  <si>
+    <t>0.9936,0.0029,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9773,0.0044,0.0027,0.0095</t>
+  </si>
+  <si>
+    <t>0.9911,0.0053,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9873,0.0021,0.0008,0.0054</t>
+  </si>
+  <si>
+    <t>0.9935,0.0019,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9788,0.0159,0.0096,0.0005</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9969,0.0004,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9936,0.0010,0.0011,0.0017</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9949,0.0014,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9929,0.0024,0.0021,0.0006</t>
+  </si>
+  <si>
+    <t>0.9920,0.0026,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9957,0.0009,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.0036,0.0014,0.9853,0.0148</t>
+  </si>
+  <si>
+    <t>0.0182,0.0021,0.9852,0.0010</t>
+  </si>
+  <si>
+    <t>0.9882,0.0008,0.0136,0.0001</t>
+  </si>
+  <si>
+    <t>0.1242,0.0004,0.9643,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.9933,0.0029,0.0026</t>
+  </si>
+  <si>
+    <t>0.0038,0.9941,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.0062,0.9884,0.0045,0.0033</t>
+  </si>
+  <si>
+    <t>0.0210,0.9688,0.0157,0.0015</t>
+  </si>
+  <si>
+    <t>0.0057,0.9916,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.0012,0.9976,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.4973,0.6436,0.0047,0.0016</t>
+  </si>
+  <si>
+    <t>0.9010,0.0336,0.0352,0.0156</t>
+  </si>
+  <si>
+    <t>0.2647,0.0040,0.8340,0.0033</t>
+  </si>
+  <si>
+    <t>0.7991,0.0203,0.2127,0.0039</t>
+  </si>
+  <si>
+    <t>0.2416,0.0719,0.6883,0.0048</t>
+  </si>
+  <si>
+    <t>0.0452,0.1082,0.0450,0.9347</t>
+  </si>
+  <si>
+    <t>0.0016,0.9954,0.0033,0.0009</t>
+  </si>
+  <si>
+    <t>0.0013,0.9954,0.0026,0.0038</t>
+  </si>
+  <si>
+    <t>0.0007,0.9931,0.0052,0.0138</t>
+  </si>
+  <si>
+    <t>0.0011,0.9317,0.9307,0.0008</t>
+  </si>
+  <si>
+    <t>0.0012,0.9975,0.0056,0.0003</t>
+  </si>
+  <si>
+    <t>0.6260,0.5240,0.0081,0.0014</t>
+  </si>
+  <si>
+    <t>0.8339,0.2632,0.0039,0.0018</t>
+  </si>
+  <si>
+    <t>0.9926,0.0015,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9828,0.0049,0.0060,0.0031</t>
+  </si>
+  <si>
+    <t>0.9948,0.0008,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.9600,0.0196,0.0133,0.0044</t>
+  </si>
+  <si>
+    <t>0.9955,0.0002,0.0004,0.0021</t>
+  </si>
+  <si>
+    <t>0.9926,0.0007,0.0015,0.0021</t>
+  </si>
+  <si>
+    <t>0.9786,0.0056,0.0131,0.0021</t>
+  </si>
+  <si>
+    <t>0.9757,0.0024,0.0186,0.0030</t>
+  </si>
+  <si>
+    <t>0.0076,0.1887,0.9799,0.0008</t>
+  </si>
+  <si>
+    <t>0.0026,0.8932,0.8606,0.0012</t>
+  </si>
+  <si>
+    <t>0.0188,0.1919,0.8610,0.0001</t>
+  </si>
+  <si>
+    <t>0.0479,0.0042,0.9541,0.0009</t>
+  </si>
+  <si>
+    <t>0.9602,0.0053,0.0198,0.0043</t>
+  </si>
+  <si>
+    <t>0.6912,0.0177,0.3626,0.0100</t>
+  </si>
+  <si>
+    <t>0.0669,0.0066,0.9531,0.0037</t>
+  </si>
+  <si>
+    <t>0.9417,0.0036,0.0640,0.0019</t>
+  </si>
+  <si>
+    <t>0.0211,0.0024,0.0129,0.9808</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0028,0.9994</t>
+  </si>
+  <si>
+    <t>0.0011,0.0067,0.0026,0.9977</t>
+  </si>
+  <si>
+    <t>0.0033,0.0005,0.0021,0.9970</t>
+  </si>
+  <si>
+    <t>0.0052,0.8590,0.8656,0.0035</t>
+  </si>
+  <si>
+    <t>0.9874,0.0042,0.0041,0.0010</t>
+  </si>
+  <si>
+    <t>0.3571,0.7743,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.9902,0.0025,0.0021,0.0019</t>
+  </si>
+  <si>
+    <t>0.0852,0.9284,0.0009,0.0025</t>
+  </si>
+  <si>
+    <t>0.9759,0.0045,0.0196,0.0024</t>
+  </si>
+  <si>
+    <t>0.7699,0.0020,0.0089,0.3030</t>
+  </si>
+  <si>
+    <t>0.9937,0.0013,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.0007,0.1062,0.9912,0.0083</t>
+  </si>
+  <si>
+    <t>0.9956,0.0004,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9410,0.0078,0.0167,0.0359</t>
+  </si>
+  <si>
+    <t>0.8825,0.1400,0.0116,0.0066</t>
+  </si>
+  <si>
+    <t>0.9620,0.0066,0.0064,0.0119</t>
+  </si>
+  <si>
+    <t>0.9435,0.0370,0.0177,0.0028</t>
+  </si>
+  <si>
+    <t>0.3159,0.7221,0.0266,0.0032</t>
+  </si>
+  <si>
+    <t>0.5322,0.4055,0.0691,0.0079</t>
+  </si>
+  <si>
+    <t>0.9669,0.0331,0.0034,0.0010</t>
+  </si>
+  <si>
+    <t>0.9939,0.0008,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.9958,0.0004,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9911,0.0027,0.0012,0.0017</t>
+  </si>
+  <si>
+    <t>0.9882,0.0003,0.0007,0.0113</t>
+  </si>
+  <si>
+    <t>0.9931,0.0011,0.0031,0.0009</t>
+  </si>
+  <si>
+    <t>0.9753,0.0176,0.0060,0.0016</t>
+  </si>
+  <si>
+    <t>0.9951,0.0015,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.7185,0.3973,0.0076,0.0034</t>
+  </si>
+  <si>
+    <t>0.6690,0.5188,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.3059,0.7954,0.0094,0.0010</t>
+  </si>
+  <si>
+    <t>0.8481,0.1611,0.0185,0.0127</t>
+  </si>
+  <si>
+    <t>0.9878,0.0098,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9059,0.1113,0.0191,0.0023</t>
+  </si>
+  <si>
+    <t>0.9908,0.0038,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.6918,0.4289,0.0016,0.0030</t>
+  </si>
+  <si>
+    <t>0.0006,0.0920,0.9980,0.0004</t>
+  </si>
+  <si>
+    <t>0.6823,0.3923,0.0207,0.0079</t>
+  </si>
+  <si>
+    <t>0.0057,0.0060,0.9910,0.0019</t>
+  </si>
+  <si>
+    <t>0.0145,0.0275,0.9735,0.0089</t>
+  </si>
+  <si>
+    <t>0.0035,0.0007,0.9975,0.0002</t>
+  </si>
+  <si>
+    <t>0.0102,0.1296,0.9613,0.0023</t>
+  </si>
+  <si>
+    <t>0.0027,0.0017,0.9940,0.0015</t>
+  </si>
+  <si>
+    <t>0.0039,0.0007,0.9958,0.0005</t>
+  </si>
+  <si>
+    <t>0.0019,0.0021,0.9953,0.0013</t>
+  </si>
+  <si>
+    <t>0.5675,0.0021,0.6052,0.0031</t>
+  </si>
+  <si>
+    <t>0.0318,0.1029,0.9314,0.0065</t>
+  </si>
+  <si>
+    <t>0.3684,0.1216,0.5365,0.0118</t>
+  </si>
+  <si>
+    <t>0.3232,0.1550,0.2955,0.0002</t>
+  </si>
+  <si>
+    <t>0.0865,0.1215,0.7947,0.0014</t>
+  </si>
+  <si>
+    <t>0.5760,0.0123,0.5334,0.0064</t>
+  </si>
+  <si>
+    <t>0.2726,0.0023,0.8492,0.0032</t>
+  </si>
+  <si>
+    <t>0.5660,0.0991,0.3195,0.0370</t>
+  </si>
+  <si>
+    <t>0.0434,0.9656,0.0025,0.0011</t>
+  </si>
+  <si>
+    <t>0.0686,0.9397,0.0056,0.0023</t>
+  </si>
+  <si>
+    <t>0.7250,0.4612,0.0049,0.0013</t>
+  </si>
+  <si>
+    <t>0.8876,0.1904,0.0020,0.0012</t>
+  </si>
+  <si>
+    <t>0.1540,0.9171,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.5386,0.4411,0.0189,0.0012</t>
+  </si>
+  <si>
+    <t>0.9528,0.0023,0.0693,0.0004</t>
+  </si>
+  <si>
+    <t>0.9619,0.0114,0.0085,0.0041</t>
+  </si>
+  <si>
+    <t>0.9603,0.0038,0.0193,0.0081</t>
+  </si>
+  <si>
+    <t>0.7391,0.0039,0.3650,0.0050</t>
+  </si>
+  <si>
+    <t>0.0049,0.0255,0.9755,0.0075</t>
+  </si>
+  <si>
+    <t>0.0201,0.0590,0.9396,0.0112</t>
+  </si>
+  <si>
+    <t>0.1666,0.0099,0.8454,0.0130</t>
+  </si>
+  <si>
+    <t>0.0114,0.0057,0.9702,0.0054</t>
+  </si>
+  <si>
+    <t>0.0015,0.8560,0.8383,0.0001</t>
+  </si>
+  <si>
+    <t>0.9958,0.0004,0.0004,0.0017</t>
+  </si>
+  <si>
+    <t>0.9888,0.0038,0.0037,0.0015</t>
+  </si>
+  <si>
+    <t>0.9855,0.0091,0.0032,0.0008</t>
+  </si>
+  <si>
+    <t>0.9910,0.0068,0.0019,0.0004</t>
+  </si>
+  <si>
+    <t>0.9324,0.1013,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.9940,0.0022,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.9881,0.0022,0.0009,0.0054</t>
+  </si>
+  <si>
+    <t>0.9926,0.0014,0.0011,0.0019</t>
+  </si>
+  <si>
+    <t>0.0078,0.0142,0.9864,0.0031</t>
+  </si>
+  <si>
+    <t>0.0622,0.2678,0.8052,0.0189</t>
+  </si>
+  <si>
+    <t>0.7665,0.0028,0.1213,0.0465</t>
+  </si>
+  <si>
+    <t>0.0180,0.0032,0.9902,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0191,0.9962,0.0037</t>
+  </si>
+  <si>
+    <t>0.0118,0.0075,0.9809,0.0039</t>
+  </si>
+  <si>
+    <t>0.0003,0.0008,0.9990,0.0006</t>
+  </si>
+  <si>
+    <t>0.0271,0.0095,0.9593,0.0049</t>
+  </si>
+  <si>
+    <t>0.0005,0.0003,0.9986,0.0006</t>
+  </si>
+  <si>
+    <t>0.0338,0.0472,0.9190,0.0182</t>
+  </si>
+  <si>
+    <t>0.0082,0.0126,0.9696,0.0025</t>
+  </si>
+  <si>
+    <t>0.9749,0.0010,0.0262,0.0007</t>
+  </si>
+  <si>
+    <t>0.5145,0.0010,0.7347,0.0007</t>
+  </si>
+  <si>
+    <t>0.9810,0.0010,0.0155,0.0012</t>
+  </si>
+  <si>
+    <t>0.9850,0.0136,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9833,0.0167,0.0024,0.0012</t>
+  </si>
+  <si>
+    <t>0.9921,0.0035,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9936,0.0017,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.9929,0.0009,0.0011,0.0024</t>
+  </si>
+  <si>
+    <t>0.9888,0.0108,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9875,0.0132,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9870,0.0027,0.0014,0.0048</t>
+  </si>
+  <si>
+    <t>0.0036,0.0031,0.9930,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0324,0.9945,0.0010</t>
+  </si>
+  <si>
+    <t>0.0030,0.0157,0.9934,0.0017</t>
+  </si>
+  <si>
+    <t>0.0537,0.0101,0.9469,0.0024</t>
+  </si>
+  <si>
+    <t>0.0115,0.0008,0.9875,0.0015</t>
+  </si>
+  <si>
+    <t>0.0555,0.0262,0.8931,0.0625</t>
+  </si>
+  <si>
+    <t>0.0475,0.1137,0.8794,0.0112</t>
+  </si>
+  <si>
+    <t>0.2934,0.0173,0.7116,0.0136</t>
+  </si>
+  <si>
+    <t>0.9660,0.0005,0.0008,0.0395</t>
+  </si>
+  <si>
+    <t>0.0247,0.0030,0.0010,0.9885</t>
+  </si>
+  <si>
+    <t>0.2021,0.0005,0.0028,0.9095</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.0004,0.9993</t>
+  </si>
+  <si>
+    <t>0.0011,0.0005,0.0018,0.9984</t>
+  </si>
+  <si>
+    <t>0.7327,0.0111,0.0024,0.2685</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2222,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2376,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,10 +2390,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2432,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2446,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,10 +2544,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,10 +2586,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,10 +2614,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2670,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2701,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2754,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,10 +2824,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2852,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2880,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2908,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2936,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2953,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2978,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2995,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3093,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3104,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3149,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3412,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3443,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,10 +3468,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,10 +3482,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,10 +3510,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3538,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3653,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3667,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3678,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3692,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3863,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3877,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4003,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4056,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4112,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4196,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4364,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4378,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4504,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,10 +4560,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4633,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4658,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4672,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4756,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5123,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5148,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5165,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5190,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5431,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
